--- a/r4-ELGA-AustrianPatientSummary-55-56---create-examples-for-each-at-aps-profile/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-55-56---create-examples-for-each-at-aps-profile/StructureDefinition-at-aps-observationresultslaboratorypathology.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-11T12:31:41+00:00</t>
+    <t>2026-01-28T09:02:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -516,7 +516,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-careplan|DeviceRequest|ImmunizationRecommendation|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-medicationrequest|NutritionOrder|ServiceRequest)
 </t>
   </si>
   <si>
@@ -545,7 +545,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-medicationadministration|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-medicationdispense|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-medicationstatement|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-procedure|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-immunization|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-imagingstudy)
 </t>
   </si>
   <si>
@@ -684,7 +684,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|Group|Device|Location)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|Group|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-device|Location)
 </t>
   </si>
   <si>
@@ -1105,7 +1105,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-device|DeviceMetric)
 </t>
   </si>
   <si>
@@ -1345,7 +1345,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|Observation|4.0.1|MolecularSequence|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-documentreference|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-imagingstudy|Media|QuestionnaireResponse|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-observation|MolecularSequence)
 </t>
   </si>
   <si>
@@ -1767,7 +1767,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="245.62890625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
